--- a/output/Data and Chart Outputs/south_korea_lng_imports_monthly.xlsx
+++ b/output/Data and Chart Outputs/south_korea_lng_imports_monthly.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -984,7 +985,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -999,7 +999,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1079,7 +1078,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -1108,7 +1107,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -1137,7 +1136,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -1166,7 +1165,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -1195,7 +1194,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -1224,7 +1223,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -1253,7 +1252,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -1282,7 +1281,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -1311,7 +1310,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -1340,7 +1339,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -1369,7 +1368,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -1398,7 +1397,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -1427,7 +1426,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -1456,7 +1455,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -1485,7 +1484,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -1514,7 +1513,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -1543,7 +1542,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -1572,7 +1571,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -1601,7 +1600,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -1630,7 +1629,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -1659,7 +1658,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -1688,7 +1687,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -1717,7 +1716,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -1746,7 +1745,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -1775,7 +1774,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -1804,7 +1803,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -1833,7 +1832,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -1862,7 +1861,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -1891,7 +1890,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -1920,7 +1919,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -1949,7 +1948,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -1978,7 +1977,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -2007,7 +2006,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -2036,7 +2035,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -2065,7 +2064,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -2094,7 +2093,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -2123,7 +2122,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -2152,7 +2151,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -2181,7 +2180,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -2210,7 +2209,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -2239,7 +2238,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -2268,7 +2267,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -2297,7 +2296,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -2326,7 +2325,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -2355,7 +2354,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -2384,7 +2383,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -2413,7 +2412,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -2442,7 +2441,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -2471,7 +2470,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -2500,7 +2499,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -2529,7 +2528,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -2558,7 +2557,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -2587,7 +2586,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -2616,7 +2615,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -2645,7 +2644,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -2674,7 +2673,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -2703,7 +2702,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -2732,7 +2731,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -2761,7 +2760,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -2790,7 +2789,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -2819,7 +2818,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -2848,7 +2847,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -2877,7 +2876,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -2906,7 +2905,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -2935,7 +2934,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -2964,7 +2963,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -2993,7 +2992,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -3022,7 +3021,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -3051,7 +3050,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -3080,7 +3079,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="5" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -3109,7 +3108,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="5" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -3138,7 +3137,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="5" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -3167,7 +3166,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -3196,7 +3195,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -3225,7 +3224,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -3254,7 +3253,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -3283,7 +3282,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -3312,7 +3311,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -3341,7 +3340,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -3370,7 +3369,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -3399,7 +3398,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
+      <c r="A82" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -3428,7 +3427,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
+      <c r="A83" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -3457,7 +3456,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -3486,7 +3485,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -3515,7 +3514,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
+      <c r="A86" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -3544,7 +3543,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
+      <c r="A87" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -3573,7 +3572,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
+      <c r="A88" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -3602,7 +3601,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -3631,7 +3630,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -3660,7 +3659,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
+      <c r="A91" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -3689,7 +3688,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -3718,7 +3717,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
+      <c r="A93" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -3747,7 +3746,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
+      <c r="A94" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -3776,7 +3775,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
+      <c r="A95" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -3805,7 +3804,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
+      <c r="A96" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -3834,7 +3833,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
+      <c r="A97" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -3863,7 +3862,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
+      <c r="A98" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -3892,7 +3891,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n">
+      <c r="A99" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -3921,7 +3920,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
+      <c r="A100" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -3950,7 +3949,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
+      <c r="A101" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -3979,7 +3978,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n">
+      <c r="A102" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -4008,7 +4007,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
+      <c r="A103" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -4037,7 +4036,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n">
+      <c r="A104" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -4066,7 +4065,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
+      <c r="A105" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -4095,7 +4094,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n">
+      <c r="A106" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -4124,7 +4123,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n">
+      <c r="A107" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -4153,7 +4152,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n">
+      <c r="A108" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -4182,7 +4181,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
+      <c r="A109" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -4211,7 +4210,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n">
+      <c r="A110" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -4240,7 +4239,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
+      <c r="A111" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -4269,7 +4268,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
+      <c r="A112" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -4298,7 +4297,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n">
+      <c r="A113" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -4327,7 +4326,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n">
+      <c r="A114" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -4356,7 +4355,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
+      <c r="A115" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -4385,7 +4384,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
+      <c r="A116" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -4414,7 +4413,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
+      <c r="A117" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -4443,7 +4442,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n">
+      <c r="A118" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -4472,7 +4471,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
+      <c r="A119" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -4501,7 +4500,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n">
+      <c r="A120" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -4530,7 +4529,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
+      <c r="A121" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -4559,7 +4558,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
+      <c r="A122" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -4588,7 +4587,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
+      <c r="A123" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -4617,7 +4616,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
+      <c r="A124" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -4646,7 +4645,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
+      <c r="A125" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -4675,7 +4674,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n">
+      <c r="A126" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -4704,7 +4703,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
+      <c r="A127" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -4733,7 +4732,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
+      <c r="A128" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -4762,7 +4761,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n">
+      <c r="A129" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -4791,7 +4790,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n">
+      <c r="A130" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -4820,7 +4819,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n">
+      <c r="A131" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -4849,7 +4848,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n">
+      <c r="A132" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -4878,7 +4877,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n">
+      <c r="A133" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -4907,7 +4906,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n">
+      <c r="A134" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -4966,7 +4965,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -4974,7 +4973,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -4982,7 +4981,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -4990,7 +4989,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -4998,7 +4997,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -5006,7 +5005,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -5014,7 +5013,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -5022,7 +5021,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -5030,7 +5029,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -5038,7 +5037,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -5046,7 +5045,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -5054,7 +5053,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -5062,7 +5061,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -5070,7 +5069,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -5078,7 +5077,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -5086,7 +5085,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -5094,7 +5093,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -5102,7 +5101,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -5110,7 +5109,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -5118,7 +5117,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -5126,7 +5125,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -5134,7 +5133,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -5142,7 +5141,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -5150,7 +5149,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -5158,7 +5157,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -5166,7 +5165,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -5174,7 +5173,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -5182,7 +5181,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -5190,7 +5189,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -5198,7 +5197,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -5206,7 +5205,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -5214,7 +5213,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -5222,7 +5221,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -5230,7 +5229,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -5238,7 +5237,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -5246,7 +5245,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -5254,7 +5253,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -5262,7 +5261,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -5270,7 +5269,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -5278,7 +5277,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -5286,7 +5285,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -5294,7 +5293,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -5302,7 +5301,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -5310,7 +5309,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -5318,7 +5317,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -5326,7 +5325,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -5334,7 +5333,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -5342,7 +5341,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -5350,7 +5349,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -5358,7 +5357,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -5366,7 +5365,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -5374,7 +5373,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -5382,7 +5381,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -5390,7 +5389,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -5398,7 +5397,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -5406,7 +5405,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -5414,7 +5413,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -5422,7 +5421,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -5430,7 +5429,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -5438,7 +5437,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -5446,7 +5445,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -5454,7 +5453,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -5462,7 +5461,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -5470,7 +5469,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -5478,7 +5477,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -5486,7 +5485,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -5494,7 +5493,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -5502,7 +5501,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -5510,7 +5509,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -5518,7 +5517,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="5" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -5526,7 +5525,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="5" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -5534,7 +5533,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="5" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -5542,7 +5541,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -5550,7 +5549,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -5558,7 +5557,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -5566,7 +5565,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -5574,7 +5573,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -5582,7 +5581,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -5590,7 +5589,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -5598,7 +5597,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -5606,7 +5605,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
+      <c r="A82" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -5614,7 +5613,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
+      <c r="A83" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -5622,7 +5621,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -5630,7 +5629,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -5638,7 +5637,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
+      <c r="A86" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -5646,7 +5645,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
+      <c r="A87" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -5654,7 +5653,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
+      <c r="A88" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -5662,7 +5661,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -5670,7 +5669,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -5678,7 +5677,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
+      <c r="A91" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -5686,7 +5685,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -5694,7 +5693,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
+      <c r="A93" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -5702,7 +5701,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
+      <c r="A94" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -5710,7 +5709,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
+      <c r="A95" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -5718,7 +5717,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
+      <c r="A96" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -5726,7 +5725,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
+      <c r="A97" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -5734,7 +5733,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
+      <c r="A98" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -5742,7 +5741,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n">
+      <c r="A99" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -5750,7 +5749,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
+      <c r="A100" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -5758,7 +5757,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
+      <c r="A101" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -5766,7 +5765,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n">
+      <c r="A102" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -5774,7 +5773,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
+      <c r="A103" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -5782,7 +5781,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n">
+      <c r="A104" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -5790,7 +5789,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
+      <c r="A105" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -5798,7 +5797,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n">
+      <c r="A106" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -5806,7 +5805,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n">
+      <c r="A107" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -5814,7 +5813,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n">
+      <c r="A108" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -5822,7 +5821,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
+      <c r="A109" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -5830,7 +5829,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n">
+      <c r="A110" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -5838,7 +5837,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
+      <c r="A111" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -5846,7 +5845,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
+      <c r="A112" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -5854,7 +5853,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n">
+      <c r="A113" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -5862,7 +5861,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n">
+      <c r="A114" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -5870,7 +5869,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
+      <c r="A115" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -5878,7 +5877,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
+      <c r="A116" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -5886,7 +5885,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
+      <c r="A117" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -5894,7 +5893,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n">
+      <c r="A118" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -5902,7 +5901,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
+      <c r="A119" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -5910,7 +5909,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n">
+      <c r="A120" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -5918,7 +5917,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
+      <c r="A121" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -5926,7 +5925,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
+      <c r="A122" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -5934,7 +5933,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
+      <c r="A123" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -5942,7 +5941,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
+      <c r="A124" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -5950,7 +5949,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
+      <c r="A125" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -5958,7 +5957,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n">
+      <c r="A126" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -5966,7 +5965,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
+      <c r="A127" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -5974,7 +5973,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
+      <c r="A128" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -5982,7 +5981,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n">
+      <c r="A129" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -5990,7 +5989,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n">
+      <c r="A130" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -5998,7 +5997,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n">
+      <c r="A131" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -6006,7 +6005,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n">
+      <c r="A132" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -6014,7 +6013,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n">
+      <c r="A133" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -6022,7 +6021,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n">
+      <c r="A134" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
